--- a/orgaos_nao_mapeados.xlsx
+++ b/orgaos_nao_mapeados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CREFITO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SEDE</t>
+          <t>DMAES PONTE NOVA</t>
         </is>
       </c>
     </row>
